--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1358,7 +1219,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -2972,7 +2833,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3556,7 +3417,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -5142,7 +5003,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5280,7 +5141,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5376,7 +5237,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6370,7 +6231,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6846,7 +6707,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -7514,7 +7375,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7560,7 +7421,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7940,7 +7801,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -8032,7 +7893,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -8504,7 +8365,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8976,7 +8837,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -9878,7 +9739,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -10868,11 +10729,11 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
-        <v>7085200</v>
+        <v>7085000</v>
       </c>
       <c r="I215" s="5" t="n">
         <v>20962</v>
@@ -11344,7 +11205,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11682,7 +11543,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11820,7 +11681,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11912,7 +11773,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -12772,7 +12633,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -13324,2479 +13185,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>首岸第4期 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>264 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>55 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>78 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>124 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$848万
-$25,089/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$769万
-$22,421/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,485万
-$25,390/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$763万
-$22,567/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$854万
-$24,820/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$841万
-$24,507/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$760万
-$22,483/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$850万
-$24,724/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$845万
-$24,699/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$836万
-$24,370/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,466万
-$25,056/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$757万
-$22,389/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$848万
-$24,637/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$842万
-$24,614/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$832万
-$24,251/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$827万
-$24,456/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$845万
-$24,552/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$805万
-$23,551/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$828万
-$24,146/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M11" s="18" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,066万
-$22,721/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,440万
-$24,612/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$765万
-$22,628/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$839万
-$24,401/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$835万
-$24,427/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$762万
-$22,268/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$838万
-$24,572/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$824万
-$24,023/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$745万
-$22,031/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$757万
-$22,020/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$828万
-$24,225/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$755万
-$22,082/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$832万
-$24,405/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$821万
-$23,939/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,280万
-$21,874/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$741万
-$21,937/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$752万
-$21,848/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$822万
-$24,038/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$824万
-$24,082/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$826万
-$24,220/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-$939万
-$24,077/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$818万
-$23,860/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,037万
-$22,102/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,270万
-$21,705/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$738万
-$21,824/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$746万
-$21,692/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$817万
-$23,877/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$818万
-$23,921/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$821万
-$24,079/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$740万
-$21,585/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,128万
-$24,055/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$733万
-$21,694/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$742万
-$21,565/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$812万
-$23,734/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$740万
-$21,635/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$818万
-$23,997/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-$929万
-$23,810/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$809万
-$23,598/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,376万
-$23,518/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$730万
-$21,592/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$738万
-$21,440/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$807万
-$23,602/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$736万
-$21,513/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$814万
-$23,883/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 343呎 (2房)
-$804万
-$23,446/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$725万
-$21,452/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$733万
-$21,316/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$730万
-$21,337/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$732万
-$21,393/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$810万
-$23,748/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$916万
-$23,187/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K18" s="20" t="inlineStr"/>
-      <c r="L18" s="20" t="inlineStr"/>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,244万
-$21,257/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$721万
-$21,339/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$802万
-$23,320/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$799万
-$23,371/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$800万
-$23,406/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$732万
-$21,479/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$910万
-$23,051/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr"/>
-      <c r="L19" s="20" t="inlineStr"/>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,105万
-$23,557/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$719万
-$21,264/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$727万
-$21,128/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$796万
-$23,269/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$725万
-$21,212/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$745万
-$21,840/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$905万
-$22,919/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="inlineStr"/>
-      <c r="L20" s="20" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,357万
-$23,190/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$716万
-$21,191/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$739万
-$21,495/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$737万
-$21,548/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$738万
-$21,583/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$796万
-$23,343/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr"/>
-      <c r="L21" s="20" t="inlineStr"/>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,094万
-$23,324/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,351万
-$23,089/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$714万
-$21,113/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$737万
-$21,414/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$718万
-$21,007/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$759万
-$22,201/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$790万
-$23,158/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$852万
-$21,572/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K22" s="20" t="inlineStr"/>
-      <c r="L22" s="20" t="inlineStr"/>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$711万
-$21,040/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$718万
-$20,880/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$755万
-$22,085/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$717万
-$20,970/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$713万
-$20,911/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr"/>
-      <c r="L23" s="20" t="inlineStr"/>
-      <c r="M23" s="19" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,079万
-$23,002/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,335万
-$22,824/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$709万
-$20,962/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$716万
-$20,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$713万
-$20,861/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$715万
-$20,898/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$780万
-$22,859/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$792万
-$20,041/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K24" s="20" t="inlineStr"/>
-      <c r="L24" s="20" t="inlineStr"/>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$976万
-$20,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$706万
-$20,884/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$713万
-$20,740/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$711万
-$20,797/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$713万
-$20,834/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-$721万
-$21,139/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr"/>
-      <c r="L25" s="20" t="inlineStr"/>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,198万
-$20,477/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$740万
-$21,901/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$710万
-$20,649/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$708万
-$20,714/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$710万
-$20,749/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$864万
-$21,868/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K26" s="20" t="inlineStr"/>
-      <c r="L26" s="20" t="inlineStr"/>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$1,060万
-$22,591/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$736万
-$21,785/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$706万
-$20,536/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$705万
-$20,603/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$746万
-$21,813/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$856万
-$21,678/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr"/>
-      <c r="L27" s="20" t="inlineStr"/>
-      <c r="M27" s="18" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-$956万
-$20,390/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-$1,300万
-$22,226/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$694万
-$20,521/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$696万
-$20,231/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$700万
-$20,475/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$714万
-$20,873/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 390呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 395呎 (2房)
-$850万
-$21,527/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr"/>
-      <c r="L28" s="20" t="inlineStr"/>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>M | 469呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 585呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$688万
-$20,357/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 344呎 (2房)
-$703万
-$20,449/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 342呎 (2房)
-$764万
-$22,342/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 342呎 (2房)
-$705万
-$20,618/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 341呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 338呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 358呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr"/>
-      <c r="L29" s="20" t="inlineStr"/>
-      <c r="M29" s="16" t="inlineStr">
-        <is>
-          <t>M | 429呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +147,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +228,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -13185,4 +13372,2479 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$848万
+$25,089/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$769万
+$22,421/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1485万
+$25,390/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$763万
+$22,567/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$854万
+$24,820/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$841万
+$24,507/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$760万
+$22,483/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$850万
+$24,724/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$845万
+$24,699/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$836万
+$24,370/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1466万
+$25,056/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$757万
+$22,389/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$848万
+$24,637/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$842万
+$24,614/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$832万
+$24,251/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$827万
+$24,456/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$845万
+$24,552/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$805万
+$23,551/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$828万
+$24,146/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1066万
+$22,721/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1440万
+$24,612/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$765万
+$22,628/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$839万
+$24,401/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$835万
+$24,427/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$762万
+$22,268/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$838万
+$24,572/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$824万
+$24,023/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$745万
+$22,031/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$757万
+$22,020/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$828万
+$24,225/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$755万
+$22,082/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$832万
+$24,405/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$821万
+$23,939/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1280万
+$21,874/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$741万
+$21,937/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$752万
+$21,848/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$822万
+$24,038/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$824万
+$24,082/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$826万
+$24,220/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+$939万
+$24,077/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$818万
+$23,860/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1037万
+$22,102/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1270万
+$21,705/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$738万
+$21,824/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$746万
+$21,692/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$817万
+$23,877/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$818万
+$23,921/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$821万
+$24,079/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$740万
+$21,585/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1128万
+$24,055/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$733万
+$21,694/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$742万
+$21,565/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$812万
+$23,734/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$740万
+$21,635/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$818万
+$23,997/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+$929万
+$23,810/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$809万
+$23,598/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1376万
+$23,518/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$730万
+$21,592/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$738万
+$21,440/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$807万
+$23,602/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$736万
+$21,513/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$814万
+$23,883/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 343呎 (2房)
+$804万
+$23,446/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$725万
+$21,452/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$733万
+$21,316/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$730万
+$21,337/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$732万
+$21,393/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$810万
+$23,748/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$916万
+$23,187/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K17" s="24" t="inlineStr"/>
+      <c r="L17" s="24" t="inlineStr"/>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1244万
+$21,257/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$721万
+$21,339/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$802万
+$23,320/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$799万
+$23,371/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$800万
+$23,406/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$732万
+$21,479/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$910万
+$23,051/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K18" s="24" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr"/>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1105万
+$23,557/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$719万
+$21,264/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$727万
+$21,128/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$796万
+$23,269/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$725万
+$21,212/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$745万
+$21,840/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$905万
+$22,919/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K19" s="24" t="inlineStr"/>
+      <c r="L19" s="24" t="inlineStr"/>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1357万
+$23,190/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$716万
+$21,191/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$739万
+$21,495/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$737万
+$21,548/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$738万
+$21,583/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$796万
+$23,343/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
+      <c r="L20" s="24" t="inlineStr"/>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1094万
+$23,324/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1351万
+$23,089/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$714万
+$21,113/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$737万
+$21,414/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$718万
+$21,007/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$759万
+$22,201/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$790万
+$23,158/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$852万
+$21,572/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K21" s="24" t="inlineStr"/>
+      <c r="L21" s="24" t="inlineStr"/>
+      <c r="M21" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$711万
+$21,040/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$718万
+$20,880/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$755万
+$22,085/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$717万
+$20,970/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$713万
+$20,911/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr"/>
+      <c r="M22" s="23" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1079万
+$23,002/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1335万
+$22,824/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$708万
+$20,962/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$716万
+$20,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$713万
+$20,861/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$715万
+$20,898/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$780万
+$22,859/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$792万
+$20,041/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K23" s="24" t="inlineStr"/>
+      <c r="L23" s="24" t="inlineStr"/>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$976万
+$20,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$706万
+$20,884/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$713万
+$20,740/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$711万
+$20,797/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$713万
+$20,834/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+$721万
+$21,139/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K24" s="24" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr"/>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1198万
+$20,477/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$740万
+$21,901/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$710万
+$20,649/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$708万
+$20,714/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$710万
+$20,749/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$864万
+$21,868/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr"/>
+      <c r="L25" s="24" t="inlineStr"/>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$1060万
+$22,591/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$736万
+$21,785/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$706万
+$20,536/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$705万
+$20,603/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$746万
+$21,813/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$856万
+$21,678/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr"/>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+$956万
+$20,390/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+$1300万
+$22,226/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$694万
+$20,521/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$696万
+$20,231/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$700万
+$20,475/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$714万
+$20,873/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 390呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 395呎 (2房)
+$850万
+$21,527/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr"/>
+      <c r="L27" s="24" t="inlineStr"/>
+      <c r="M27" s="20" t="inlineStr">
+        <is>
+          <t>M | 469呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 585呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$688万
+$20,357/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 344呎 (2房)
+$703万
+$20,449/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 342呎 (2房)
+$764万
+$22,342/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 342呎 (2房)
+$705万
+$20,618/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 341呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 338呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 358呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr"/>
+      <c r="L28" s="24" t="inlineStr"/>
+      <c r="M28" s="20" t="inlineStr">
+        <is>
+          <t>M | 429呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -661,7 +661,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -14173,7 +14173,7 @@
           <t>B | 338呎 (2房)
 $765万
 $22,628/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -14379,7 +14379,7 @@
           <t>B | 338呎 (2房)
 $741万
 $21,937/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -14387,7 +14387,7 @@
           <t>C | 344呎 (2房)
 $752万
 $21,848/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -14712,7 +14712,7 @@
           <t>E | 342呎 (2房)
 $736万
 $21,513/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -15592,7 +15592,7 @@
           <t>B | 338呎 (2房)
 $736万
 $21,785/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -121,13 +121,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -274,10 +274,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:N266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -721,6 +725,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -771,6 +795,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -821,6 +865,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -871,6 +935,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -921,6 +1005,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -971,6 +1075,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1021,6 +1145,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1071,6 +1215,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1121,6 +1285,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1171,6 +1355,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1221,6 +1425,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1271,6 +1495,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1321,6 +1565,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1371,6 +1635,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1417,6 +1701,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7690400</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>22421</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1467,6 +1767,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1517,6 +1837,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1567,6 +1907,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1617,6 +1977,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1667,6 +2047,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1717,6 +2117,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1767,6 +2187,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1817,6 +2257,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1847,21 +2307,37 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>8480000</v>
+        <v>7716800</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>25089</v>
+        <v>22831</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>7716800</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>22831</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1913,6 +2389,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1963,6 +2459,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2009,6 +2525,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7649460</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>22302</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2059,6 +2591,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2109,6 +2661,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2159,6 +2731,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2209,6 +2801,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2259,6 +2871,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2309,6 +2941,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2359,6 +3011,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2405,6 +3077,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7769580</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>22586</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2451,6 +3139,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>7627600</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>22567</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2497,6 +3201,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>13516230</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>23105</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2547,6 +3267,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2593,6 +3333,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7606690</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>22177</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2643,6 +3399,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2693,6 +3469,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2743,6 +3539,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2793,6 +3609,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2843,6 +3679,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2893,6 +3749,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2939,6 +3815,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7686770</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>22476</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2985,6 +3877,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>7739550</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>22499</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3031,6 +3939,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>7599400</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>22483</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3081,6 +4005,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3131,6 +4075,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3177,6 +4141,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>7569380</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>22068</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3227,6 +4207,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3277,6 +4277,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3327,6 +4347,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3377,6 +4417,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3427,6 +4487,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3477,6 +4557,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3523,6 +4623,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>7660380</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>22399</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3569,6 +4685,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>7712250</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>22419</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3615,6 +4747,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>7567500</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>22389</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3661,6 +4809,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>13338780</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>22801</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3707,6 +4871,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>10656100</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>22721</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3753,6 +4933,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>7536620</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21973</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3803,6 +4999,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3853,6 +5069,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3903,6 +5139,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3953,6 +5209,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4003,6 +5279,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4053,6 +5349,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4099,6 +5415,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>8054400</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>23551</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4145,6 +5477,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>7685860</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>22343</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4191,6 +5539,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>7522060</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>22255</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4241,6 +5605,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4291,6 +5675,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4337,6 +5741,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>7498400</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>21861</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4387,6 +5807,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4437,6 +5877,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4487,6 +5947,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4537,6 +6017,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4583,6 +6083,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>7624890</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>22360</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4629,6 +6145,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>7615700</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>22268</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4675,6 +6207,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>7602140</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>22228</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4721,6 +6269,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>7638540</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>22205</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4767,6 +6331,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>7648300</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>22628</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4813,6 +6393,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>13102180</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>22397</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4863,6 +6459,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4909,6 +6525,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>7472010</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>21784</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4959,6 +6591,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5009,6 +6661,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5059,6 +6731,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5109,6 +6801,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5155,6 +6867,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>7573020</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>22208</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5201,6 +6929,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>7552000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>22082</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5247,6 +6991,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>7539350</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>22045</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5282,7 +7042,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5293,6 +7053,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>7574800</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>22020</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5339,6 +7115,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>7446500</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>22031</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5389,6 +7181,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5435,6 +7247,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>10365800</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>22102</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5481,6 +7309,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>7447440</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>21713</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5531,6 +7375,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5577,6 +7441,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>8544900</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>21910</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5627,6 +7507,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5677,6 +7577,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5723,6 +7643,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>7515690</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>22040</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5769,6 +7705,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>7494760</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>21915</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5815,6 +7767,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>7481110</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>21875</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5861,6 +7829,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>7515600</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>21848</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5907,6 +7891,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>7414600</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>21937</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5953,6 +7953,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>12796400</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>21874</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5999,6 +8015,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>10266620</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>21890</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6045,6 +8077,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>7403700</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>21585</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6095,6 +8143,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6145,6 +8213,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6195,6 +8283,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6245,6 +8353,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6291,6 +8419,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>7472010</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>21912</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6337,6 +8481,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>7444710</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>21768</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6383,6 +8543,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>7431060</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>21728</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6429,6 +8605,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>7462000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>21692</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6475,6 +8667,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>7376400</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>21824</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6510,7 +8718,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6521,6 +8729,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>12697200</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>21705</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6571,6 +8795,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6617,6 +8861,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>7365540</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>21474</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6667,6 +8927,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6713,6 +8993,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>8450260</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>21667</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6763,6 +9059,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6813,6 +9129,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6859,6 +9195,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>7446530</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>21837</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6905,6 +9257,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>7399200</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>21635</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6951,6 +9319,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>7386470</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>21598</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6997,6 +9381,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>7418300</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>21565</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7043,6 +9443,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>7332700</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>21694</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7093,6 +9509,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7143,6 +9579,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7189,6 +9645,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>7318220</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>21336</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7239,6 +9711,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7289,6 +9781,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7339,6 +9851,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7389,6 +9921,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7435,6 +9987,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>7411040</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>21733</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7481,6 +10049,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>7357300</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>21513</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7527,6 +10111,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>7345520</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>21478</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7573,6 +10173,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>7375500</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>21440</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7619,6 +10235,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>7298200</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>21592</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7665,6 +10297,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>12519780</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>21401</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7715,6 +10363,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7761,6 +10429,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>8334690</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>21100</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7811,6 +10495,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7861,6 +10565,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7907,6 +10631,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>7369180</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>21610</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7953,6 +10693,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>7316400</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>21393</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7999,6 +10755,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>7297200</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>21337</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8045,6 +10817,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>7332700</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>21316</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8091,6 +10879,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>7250800</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>21452</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8141,6 +10945,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8187,6 +11011,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>10053680</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>21436</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8233,6 +11073,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>8285550</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>20976</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8283,6 +11139,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8333,6 +11209,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8379,6 +11275,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>7324500</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>21479</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8425,6 +11337,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>7284550</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>21300</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8471,6 +11399,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>7273630</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>21268</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8517,6 +11461,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>7300020</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>21221</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8563,6 +11523,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>7212600</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>21339</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8609,6 +11585,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>12435100</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>21257</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8659,6 +11651,26 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8705,6 +11717,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>8238230</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>20856</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8755,6 +11783,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8805,6 +11853,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8840,7 +11908,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8851,6 +11919,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>7447400</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>21840</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8897,6 +11981,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>7254500</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>21212</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8943,6 +12043,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>7241780</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>21175</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8978,7 +12094,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8989,6 +12105,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>7268100</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>21128</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9035,6 +12167,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>7187100</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>21264</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9085,6 +12233,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9131,6 +12299,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>9954490</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>21225</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9181,6 +12365,26 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9231,6 +12435,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9281,6 +12505,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9327,6 +12571,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>7243600</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>21242</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9373,6 +12633,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>7381400</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>21583</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9419,6 +12695,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>7369300</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>21548</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9465,6 +12757,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>7394400</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>21495</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9500,7 +12808,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9511,6 +12819,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>7162600</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>21191</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9557,6 +12881,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>12345060</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>21103</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9607,6 +12947,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9653,6 +13013,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>8520900</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>21572</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9703,6 +13079,26 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9753,6 +13149,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9783,21 +13199,37 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>7897000</v>
+        <v>7186200</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>23158</v>
+        <v>21074</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>7186200</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>21074</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9845,6 +13277,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>7592600</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>22201</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9891,6 +13339,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>7184400</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>21007</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9937,6 +13401,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>7366500</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>21414</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9983,6 +13463,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>7136200</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>21113</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10029,6 +13525,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>12291370</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>21011</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10075,6 +13587,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>9817080</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>20932</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10125,6 +13653,26 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10175,6 +13723,26 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10225,6 +13793,26 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10271,6 +13859,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>7130700</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>20911</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10317,6 +13921,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>7171700</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>20970</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10363,6 +13983,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>7553200</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>22085</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10409,6 +14045,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>7182600</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>20880</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10455,6 +14107,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>7111600</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>21040</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10505,6 +14173,26 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10551,6 +14239,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>9755200</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>20800</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10597,6 +14301,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>7916000</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>20041</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10647,6 +14367,26 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10697,6 +14437,26 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10727,21 +14487,37 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>7795000</v>
+        <v>7483200</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>22859</v>
+        <v>21945</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>7483200</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>21945</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -10789,6 +14565,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>7147100</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>20898</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10835,6 +14627,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>7134400</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>20861</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10870,7 +14678,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10881,6 +14689,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>7155300</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>20800</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10927,6 +14751,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>7085000</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>20962</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10973,6 +14813,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>12150320</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>20770</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11023,6 +14879,26 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11073,6 +14949,26 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11123,6 +15019,26 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11173,6 +15089,26 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11208,7 +15144,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -11219,6 +15155,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>7208400</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>21139</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11265,6 +15217,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>7125300</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>20834</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11311,6 +15279,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>7112500</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>20797</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11357,6 +15341,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>7134400</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>20740</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11403,6 +15403,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>7058800</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>20884</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11453,6 +15469,26 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11499,6 +15535,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>9641450</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>20557</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11545,6 +15597,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>7860580</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>19900</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11595,6 +15663,26 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11645,6 +15733,26 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11695,6 +15803,26 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11741,6 +15869,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>7096100</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>20749</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11787,6 +15931,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7084300</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>20714</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11822,7 +15982,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11833,6 +15993,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>7103400</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>20649</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11879,6 +16055,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>7402500</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>21901</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11925,6 +16117,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>11979200</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>20477</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11971,6 +16179,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>9563100</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>20390</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12017,6 +16241,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>7792330</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>19727</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12067,6 +16307,26 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12117,6 +16377,26 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12167,6 +16447,26 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12202,7 +16502,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -12213,6 +16513,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>7460100</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>21813</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12259,6 +16575,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>7046100</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>20603</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12294,7 +16626,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -12305,6 +16637,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>7064300</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>20536</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12351,6 +16699,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>7363200</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>21785</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12401,6 +16765,26 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12451,6 +16835,26 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12497,6 +16901,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>7737730</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>19589</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12547,6 +16967,26 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12597,6 +17037,26 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12647,6 +17107,26 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12693,6 +17173,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>7138600</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>20873</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12739,6 +17235,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>7002400</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>20475</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12785,6 +17297,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>6959600</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>20231</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12831,6 +17359,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>6936000</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>20521</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12877,6 +17421,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>11831820</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>20225</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12927,6 +17487,26 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12977,6 +17557,26 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13027,6 +17627,26 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13077,6 +17697,26 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13127,6 +17767,26 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13173,6 +17833,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>7051200</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>20618</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13219,6 +17895,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>6953310</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>20331</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>100天付款計劃</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13265,6 +17957,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>7034500</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>20449</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13311,6 +18019,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>6880500</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>20357</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13361,13 +18085,33 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -13445,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -13455,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13656,9 +18400,9 @@
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
-$848万
-$25,089/呎
-(在售)</t>
+$772万
+$22,831/呎
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -13725,12 +18469,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $769万
 $22,421/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -13748,7 +18492,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1485万
@@ -13756,12 +18500,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $763万
 $22,567/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -13828,7 +18572,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $841万
@@ -13859,12 +18603,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $760万
 $22,483/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -13931,7 +18675,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $836万
@@ -13954,7 +18698,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1466万
@@ -13962,12 +18706,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $757万
 $22,389/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -14034,7 +18778,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $832万
@@ -14065,7 +18809,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $827万
@@ -14073,7 +18817,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $845万
@@ -14081,12 +18825,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $805万
 $23,551/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -14137,7 +18881,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $828万
@@ -14145,12 +18889,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1066万
 $22,721/呎
-(26年-06月)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -14160,7 +18904,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1440万
@@ -14168,15 +18912,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $765万
 $22,628/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $839万
@@ -14184,7 +18928,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $835万
@@ -14192,15 +18936,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $762万
 $22,268/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $838万
@@ -14240,7 +18984,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $824万
@@ -14271,23 +19015,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $745万
 $22,031/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $757万
 $22,020/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $828万
@@ -14295,15 +19039,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $755万
 $22,082/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $832万
@@ -14343,7 +19087,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $821万
@@ -14366,31 +19110,31 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1280万
 $21,874/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $741万
 $21,937/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $752万
 $21,848/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $822万
@@ -14398,7 +19142,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $824万
@@ -14406,7 +19150,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $826万
@@ -14430,7 +19174,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>J | 390呎 (2房)
 $939万
@@ -14446,7 +19190,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $818万
@@ -14454,12 +19198,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M13" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1037万
 $22,102/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -14469,31 +19213,31 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1270万
 $21,705/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $738万
 $21,824/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $746万
 $21,692/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $817万
@@ -14501,7 +19245,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $818万
@@ -14509,7 +19253,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $821万
@@ -14549,12 +19293,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L14" s="22" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $740万
 $21,585/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -14580,23 +19324,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $733万
 $21,694/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $742万
 $21,565/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $812万
@@ -14604,15 +19348,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $740万
 $21,635/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $818万
@@ -14636,7 +19380,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>J | 390呎 (2房)
 $929万
@@ -14652,7 +19396,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $809万
@@ -14675,7 +19419,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1376万
@@ -14683,23 +19427,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $730万
 $21,592/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $738万
 $21,440/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $807万
@@ -14707,15 +19451,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $736万
 $21,513/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $814万
@@ -14755,7 +19499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L16" s="21" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>L | 343呎 (2房)
 $804万
@@ -14786,39 +19530,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $725万
 $21,452/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $733万
 $21,316/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $730万
 $21,337/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $732万
 $21,393/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $810万
@@ -14842,7 +19586,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $916万
@@ -14867,23 +19611,23 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1244万
 $21,257/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $721万
 $21,339/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $802万
@@ -14891,7 +19635,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $799万
@@ -14899,7 +19643,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $800万
@@ -14907,12 +19651,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $732万
 $21,479/呎
-(26年-06月)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -14931,7 +19675,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $910万
@@ -14941,7 +19685,7 @@
       </c>
       <c r="K18" s="24" t="inlineStr"/>
       <c r="L18" s="24" t="inlineStr"/>
-      <c r="M18" s="21" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1105万
@@ -14964,23 +19708,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $719万
 $21,264/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $727万
 $21,128/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $796万
@@ -14988,20 +19732,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $725万
 $21,212/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $745万
 $21,840/呎
-(26年-06月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -15020,7 +19764,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $905万
@@ -15045,7 +19789,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1357万
@@ -15053,39 +19797,39 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $716万
 $21,191/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $739万
 $21,495/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $737万
 $21,548/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $738万
 $21,583/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $796万
@@ -15119,7 +19863,7 @@
       </c>
       <c r="K20" s="24" t="inlineStr"/>
       <c r="L20" s="24" t="inlineStr"/>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1094万
@@ -15134,7 +19878,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1351万
@@ -15142,44 +19886,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $714万
 $21,113/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $737万
 $21,414/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $718万
 $21,007/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $759万
 $22,201/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$790万
-$23,158/呎
-(在售)</t>
+$719万
+$21,074/呎
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -15198,12 +19942,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $852万
 $21,572/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr"/>
@@ -15231,44 +19975,44 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $711万
 $21,040/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $718万
 $20,880/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $755万
 $22,085/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $717万
 $20,970/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $713万
 $20,911/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -15312,7 +20056,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1335万
@@ -15320,44 +20064,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $708万
 $20,962/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $716万
 $20,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $713万
 $20,861/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+(26年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $715万
 $20,898/呎
-(26年-06月)</t>
+(26年-06月-13日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
-$780万
-$22,859/呎
-(在售)</t>
+$748万
+$21,945/呎
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -15376,22 +20120,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $792万
 $20,041/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr"/>
       <c r="L23" s="24" t="inlineStr"/>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="M23" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $976万
 $20,800/呎
-(26年-06月)</t>
+(26年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -15409,44 +20153,44 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $706万
 $20,884/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $713万
 $20,740/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $711万
 $20,797/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $713万
 $20,834/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 341呎 (2房)
 $721万
 $21,139/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -15490,44 +20234,44 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1198万
 $20,477/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $740万
 $21,901/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $710万
 $20,649/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $708万
 $20,714/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $710万
 $20,749/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -15554,7 +20298,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $864万
@@ -15564,7 +20308,7 @@
       </c>
       <c r="K25" s="24" t="inlineStr"/>
       <c r="L25" s="24" t="inlineStr"/>
-      <c r="M25" s="21" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $1060万
@@ -15587,36 +20331,36 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $736万
 $21,785/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $706万
 $20,536/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $705万
 $20,603/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $746万
 $21,813/呎
-(26年-06月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -15643,7 +20387,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $856万
@@ -15653,12 +20397,12 @@
       </c>
       <c r="K26" s="24" t="inlineStr"/>
       <c r="L26" s="24" t="inlineStr"/>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>M | 469呎 (2房)
 $956万
 $20,390/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -15668,7 +20412,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 585呎 (3房)
 $1300万
@@ -15676,36 +20420,36 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $694万
 $20,521/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $696万
 $20,231/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $700万
 $20,475/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $714万
 $20,873/呎
-(26年-07月)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -15732,7 +20476,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>J | 395呎 (2房)
 $850万
@@ -15765,23 +20509,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
 $688万
 $20,357/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 344呎 (2房)
 $703万
 $20,449/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
 $764万
@@ -15789,12 +20533,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
 $705万
 $20,618/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -666,7 +666,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -3201,18 +3201,18 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>13516230</v>
+        <v>13516200</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>23105</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4933,18 +4933,18 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>7536620</v>
+        <v>7536600</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>21973</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -6083,18 +6083,18 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>7624890</v>
+        <v>7624800</v>
       </c>
       <c r="L81" s="5" t="n">
         <v>22360</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -15535,18 +15535,18 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>9641450</v>
+        <v>9641400</v>
       </c>
       <c r="L227" s="5" t="n">
         <v>20557</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -18830,7 +18830,7 @@
           <t>D | 342呎 (2房)
 $805万
 $23,551/呎
-(26年-06月-17日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -20125,7 +20125,7 @@
           <t>J | 395呎 (2房)
 $792万
 $20,041/呎
-(26年-06月-17日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr"/>

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -5523,34 +5523,34 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>8266000</v>
+        <v>7522000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>24456</v>
+        <v>22254</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>7522060</v>
+        <v>7522000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>22255</v>
+        <v>22254</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -11321,34 +11321,34 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>8005000</v>
+        <v>7284500</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>23406</v>
+        <v>21300</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>7284550</v>
+        <v>7284500</v>
       </c>
       <c r="L162" s="5" t="n">
         <v>21300</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12027,34 +12027,34 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>7958000</v>
+        <v>7241700</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>23269</v>
+        <v>21175</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>7241780</v>
+        <v>7241700</v>
       </c>
       <c r="L173" s="5" t="n">
         <v>21175</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18809,12 +18809,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 338呎 (2房)
-$827万
-$24,456/呎
-(在售)</t>
+$752万
+$22,254/呎
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18894,7 +18894,7 @@
           <t>M | 469呎 (2房)
 $1066万
 $22,721/呎
-(26年-06月-30日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -19298,7 +19298,7 @@
           <t>L | 343呎 (2房)
 $740万
 $21,585/呎
-(26年-06月-28日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -19643,12 +19643,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 342呎 (2房)
-$800万
-$23,406/呎
-(在售)</t>
+$728万
+$21,300/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -19724,12 +19724,12 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 342呎 (2房)
-$796万
-$23,269/呎
-(在售)</t>
+$724万
+$21,175/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -19737,7 +19737,7 @@
           <t>E | 342呎 (2房)
 $725万
 $21,212/呎
-(26年-07月-01日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -19947,7 +19947,7 @@
           <t>J | 395呎 (2房)
 $852万
 $21,572/呎
-(26年-06月-17日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr"/>
@@ -20433,7 +20433,7 @@
           <t>C | 344呎 (2房)
 $696万
 $20,231/呎
-(26年-06月-25日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 344呎 (2房)
 $703万
 $20,449/呎
-(26年-06月-28日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 342呎 (2房)
 $705万
 $20,618/呎
-(26年-07月-01日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -18402,7 +18402,7 @@
           <t>B | 338呎 (2房)
 $772万
 $22,831/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18474,7 +18474,7 @@
           <t>L | 343呎 (2房)
 $769万
 $22,421/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -18505,7 +18505,7 @@
           <t>B | 338呎 (2房)
 $763万
 $22,567/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -18608,7 +18608,7 @@
           <t>B | 338呎 (2房)
 $760万
 $22,483/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -18711,7 +18711,7 @@
           <t>B | 338呎 (2房)
 $757万
 $22,389/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -18814,7 +18814,7 @@
           <t>B | 338呎 (2房)
 $752万
 $22,254/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18830,7 +18830,7 @@
           <t>D | 342呎 (2房)
 $805万
 $23,551/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -18894,7 +18894,7 @@
           <t>M | 469呎 (2房)
 $1066万
 $22,721/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -18917,7 +18917,7 @@
           <t>B | 338呎 (2房)
 $765万
 $22,628/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18941,7 +18941,7 @@
           <t>E | 342呎 (2房)
 $762万
 $22,268/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -19020,7 +19020,7 @@
           <t>B | 338呎 (2房)
 $745万
 $22,031/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -19028,7 +19028,7 @@
           <t>C | 344呎 (2房)
 $757万
 $22,020/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19044,7 +19044,7 @@
           <t>E | 342呎 (2房)
 $755万
 $22,082/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19115,7 +19115,7 @@
           <t>A | 585呎 (3房)
 $1280万
 $21,874/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -19123,7 +19123,7 @@
           <t>B | 338呎 (2房)
 $741万
 $21,937/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -19131,7 +19131,7 @@
           <t>C | 344呎 (2房)
 $752万
 $21,848/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19203,7 +19203,7 @@
           <t>M | 469呎 (2房)
 $1037万
 $22,102/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
           <t>A | 585呎 (3房)
 $1270万
 $21,705/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -19226,7 +19226,7 @@
           <t>B | 338呎 (2房)
 $738万
 $21,824/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -19234,7 +19234,7 @@
           <t>C | 344呎 (2房)
 $746万
 $21,692/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19298,7 +19298,7 @@
           <t>L | 343呎 (2房)
 $740万
 $21,585/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -19329,7 +19329,7 @@
           <t>B | 338呎 (2房)
 $733万
 $21,694/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -19337,7 +19337,7 @@
           <t>C | 344呎 (2房)
 $742万
 $21,565/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19353,7 +19353,7 @@
           <t>E | 342呎 (2房)
 $740万
 $21,635/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19432,7 +19432,7 @@
           <t>B | 338呎 (2房)
 $730万
 $21,592/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -19440,7 +19440,7 @@
           <t>C | 344呎 (2房)
 $738万
 $21,440/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19456,7 +19456,7 @@
           <t>E | 342呎 (2房)
 $736万
 $21,513/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -19535,7 +19535,7 @@
           <t>B | 338呎 (2房)
 $725万
 $21,452/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -19543,7 +19543,7 @@
           <t>C | 344呎 (2房)
 $733万
 $21,316/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -19551,7 +19551,7 @@
           <t>D | 342呎 (2房)
 $730万
 $21,337/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -19559,7 +19559,7 @@
           <t>E | 342呎 (2房)
 $732万
 $21,393/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -19616,7 +19616,7 @@
           <t>A | 585呎 (3房)
 $1244万
 $21,257/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -19624,7 +19624,7 @@
           <t>B | 338呎 (2房)
 $721万
 $21,339/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19648,7 +19648,7 @@
           <t>E | 342呎 (2房)
 $728万
 $21,300/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -19656,7 +19656,7 @@
           <t>F | 341呎 (2房)
 $732万
 $21,479/呎
-(26年-06月-30日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -19713,7 +19713,7 @@
           <t>B | 338呎 (2房)
 $719万
 $21,264/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -19721,7 +19721,7 @@
           <t>C | 344呎 (2房)
 $727万
 $21,128/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -19729,7 +19729,7 @@
           <t>D | 342呎 (2房)
 $724万
 $21,175/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -19737,7 +19737,7 @@
           <t>E | 342呎 (2房)
 $725万
 $21,212/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -19745,7 +19745,7 @@
           <t>F | 341呎 (2房)
 $745万
 $21,840/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -19802,7 +19802,7 @@
           <t>B | 338呎 (2房)
 $716万
 $21,191/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19810,7 +19810,7 @@
           <t>C | 344呎 (2房)
 $739万
 $21,495/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -19818,7 +19818,7 @@
           <t>D | 342呎 (2房)
 $737万
 $21,548/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -19826,7 +19826,7 @@
           <t>E | 342呎 (2房)
 $738万
 $21,583/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -19891,7 +19891,7 @@
           <t>B | 338呎 (2房)
 $714万
 $21,113/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -19899,7 +19899,7 @@
           <t>C | 344呎 (2房)
 $737万
 $21,414/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -19907,7 +19907,7 @@
           <t>D | 342呎 (2房)
 $718万
 $21,007/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -19915,7 +19915,7 @@
           <t>E | 342呎 (2房)
 $759万
 $22,201/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -19923,7 +19923,7 @@
           <t>F | 341呎 (2房)
 $719万
 $21,074/呎
-(26年-07月-11日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -19947,7 +19947,7 @@
           <t>J | 395呎 (2房)
 $852万
 $21,572/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr"/>
@@ -19980,7 +19980,7 @@
           <t>B | 338呎 (2房)
 $711万
 $21,040/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -19988,7 +19988,7 @@
           <t>C | 344呎 (2房)
 $718万
 $20,880/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -19996,7 +19996,7 @@
           <t>D | 342呎 (2房)
 $755万
 $22,085/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -20004,7 +20004,7 @@
           <t>E | 342呎 (2房)
 $717万
 $20,970/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -20012,7 +20012,7 @@
           <t>F | 341呎 (2房)
 $713万
 $20,911/呎
-(26年-06月-26日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -20069,7 +20069,7 @@
           <t>B | 338呎 (2房)
 $708万
 $20,962/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>C | 344呎 (2房)
 $716万
 $20,800/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>D | 342呎 (2房)
 $713万
 $20,861/呎
-(26年-06月-13日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -20093,7 +20093,7 @@
           <t>E | 342呎 (2房)
 $715万
 $20,898/呎
-(26年-06月-13日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -20101,7 +20101,7 @@
           <t>F | 341呎 (2房)
 $748万
 $21,945/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -20125,7 +20125,7 @@
           <t>J | 395呎 (2房)
 $792万
 $20,041/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr"/>
@@ -20135,7 +20135,7 @@
           <t>M | 469呎 (2房)
 $976万
 $20,800/呎
-(26年-06月-13日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -20158,7 +20158,7 @@
           <t>B | 338呎 (2房)
 $706万
 $20,884/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>C | 344呎 (2房)
 $713万
 $20,740/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>D | 342呎 (2房)
 $711万
 $20,797/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -20182,7 +20182,7 @@
           <t>E | 342呎 (2房)
 $713万
 $20,834/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -20190,7 +20190,7 @@
           <t>F | 341呎 (2房)
 $721万
 $21,139/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -20239,7 +20239,7 @@
           <t>A | 585呎 (3房)
 $1198万
 $20,477/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -20247,7 +20247,7 @@
           <t>B | 338呎 (2房)
 $740万
 $21,901/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -20255,7 +20255,7 @@
           <t>C | 344呎 (2房)
 $710万
 $20,649/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -20263,7 +20263,7 @@
           <t>D | 342呎 (2房)
 $708万
 $20,714/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -20271,7 +20271,7 @@
           <t>E | 342呎 (2房)
 $710万
 $20,749/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -20336,7 +20336,7 @@
           <t>B | 338呎 (2房)
 $736万
 $21,785/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -20344,7 +20344,7 @@
           <t>C | 344呎 (2房)
 $706万
 $20,536/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -20352,7 +20352,7 @@
           <t>D | 342呎 (2房)
 $705万
 $20,603/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -20360,7 +20360,7 @@
           <t>E | 342呎 (2房)
 $746万
 $21,813/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -20402,7 +20402,7 @@
           <t>M | 469呎 (2房)
 $956万
 $20,390/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -20425,7 +20425,7 @@
           <t>B | 338呎 (2房)
 $694万
 $20,521/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -20433,7 +20433,7 @@
           <t>C | 344呎 (2房)
 $696万
 $20,231/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -20441,7 +20441,7 @@
           <t>D | 342呎 (2房)
 $700万
 $20,475/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -20449,7 +20449,7 @@
           <t>E | 342呎 (2房)
 $714万
 $20,873/呎
-(26年-07月-04日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>B | 338呎 (2房)
 $688万
 $20,357/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 344呎 (2房)
 $703万
 $20,449/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 342呎 (2房)
 $705万
 $20,618/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -18402,7 +18402,7 @@
           <t>B | 338呎 (2房)
 $772万
 $22,831/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18474,7 +18474,7 @@
           <t>L | 343呎 (2房)
 $769万
 $22,421/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -18505,7 +18505,7 @@
           <t>B | 338呎 (2房)
 $763万
 $22,567/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -18608,7 +18608,7 @@
           <t>B | 338呎 (2房)
 $760万
 $22,483/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -18711,7 +18711,7 @@
           <t>B | 338呎 (2房)
 $757万
 $22,389/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -18814,7 +18814,7 @@
           <t>B | 338呎 (2房)
 $752万
 $22,254/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18830,7 +18830,7 @@
           <t>D | 342呎 (2房)
 $805万
 $23,551/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -18894,7 +18894,7 @@
           <t>M | 469呎 (2房)
 $1066万
 $22,721/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -18917,7 +18917,7 @@
           <t>B | 338呎 (2房)
 $765万
 $22,628/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18941,7 +18941,7 @@
           <t>E | 342呎 (2房)
 $762万
 $22,268/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -19020,7 +19020,7 @@
           <t>B | 338呎 (2房)
 $745万
 $22,031/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -19028,7 +19028,7 @@
           <t>C | 344呎 (2房)
 $757万
 $22,020/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19044,7 +19044,7 @@
           <t>E | 342呎 (2房)
 $755万
 $22,082/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19115,7 +19115,7 @@
           <t>A | 585呎 (3房)
 $1280万
 $21,874/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -19123,7 +19123,7 @@
           <t>B | 338呎 (2房)
 $741万
 $21,937/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -19131,7 +19131,7 @@
           <t>C | 344呎 (2房)
 $752万
 $21,848/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19203,7 +19203,7 @@
           <t>M | 469呎 (2房)
 $1037万
 $22,102/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
           <t>A | 585呎 (3房)
 $1270万
 $21,705/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -19226,7 +19226,7 @@
           <t>B | 338呎 (2房)
 $738万
 $21,824/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -19234,7 +19234,7 @@
           <t>C | 344呎 (2房)
 $746万
 $21,692/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19298,7 +19298,7 @@
           <t>L | 343呎 (2房)
 $740万
 $21,585/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -19329,7 +19329,7 @@
           <t>B | 338呎 (2房)
 $733万
 $21,694/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -19337,7 +19337,7 @@
           <t>C | 344呎 (2房)
 $742万
 $21,565/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19353,7 +19353,7 @@
           <t>E | 342呎 (2房)
 $740万
 $21,635/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19432,7 +19432,7 @@
           <t>B | 338呎 (2房)
 $730万
 $21,592/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -19440,7 +19440,7 @@
           <t>C | 344呎 (2房)
 $738万
 $21,440/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19456,7 +19456,7 @@
           <t>E | 342呎 (2房)
 $736万
 $21,513/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -19535,7 +19535,7 @@
           <t>B | 338呎 (2房)
 $725万
 $21,452/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -19543,7 +19543,7 @@
           <t>C | 344呎 (2房)
 $733万
 $21,316/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -19551,7 +19551,7 @@
           <t>D | 342呎 (2房)
 $730万
 $21,337/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -19559,7 +19559,7 @@
           <t>E | 342呎 (2房)
 $732万
 $21,393/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -19616,7 +19616,7 @@
           <t>A | 585呎 (3房)
 $1244万
 $21,257/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -19624,7 +19624,7 @@
           <t>B | 338呎 (2房)
 $721万
 $21,339/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19648,7 +19648,7 @@
           <t>E | 342呎 (2房)
 $728万
 $21,300/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -19656,7 +19656,7 @@
           <t>F | 341呎 (2房)
 $732万
 $21,479/呎
-(26年-06月)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -19713,7 +19713,7 @@
           <t>B | 338呎 (2房)
 $719万
 $21,264/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -19721,7 +19721,7 @@
           <t>C | 344呎 (2房)
 $727万
 $21,128/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -19729,7 +19729,7 @@
           <t>D | 342呎 (2房)
 $724万
 $21,175/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -19737,7 +19737,7 @@
           <t>E | 342呎 (2房)
 $725万
 $21,212/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -19745,7 +19745,7 @@
           <t>F | 341呎 (2房)
 $745万
 $21,840/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -19802,7 +19802,7 @@
           <t>B | 338呎 (2房)
 $716万
 $21,191/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19810,7 +19810,7 @@
           <t>C | 344呎 (2房)
 $739万
 $21,495/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -19818,7 +19818,7 @@
           <t>D | 342呎 (2房)
 $737万
 $21,548/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -19826,7 +19826,7 @@
           <t>E | 342呎 (2房)
 $738万
 $21,583/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -19891,7 +19891,7 @@
           <t>B | 338呎 (2房)
 $714万
 $21,113/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -19899,7 +19899,7 @@
           <t>C | 344呎 (2房)
 $737万
 $21,414/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -19907,7 +19907,7 @@
           <t>D | 342呎 (2房)
 $718万
 $21,007/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -19915,7 +19915,7 @@
           <t>E | 342呎 (2房)
 $759万
 $22,201/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -19923,7 +19923,7 @@
           <t>F | 341呎 (2房)
 $719万
 $21,074/呎
-(26年-07月)</t>
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -19947,7 +19947,7 @@
           <t>J | 395呎 (2房)
 $852万
 $21,572/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr"/>
@@ -19980,7 +19980,7 @@
           <t>B | 338呎 (2房)
 $711万
 $21,040/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -19988,7 +19988,7 @@
           <t>C | 344呎 (2房)
 $718万
 $20,880/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -19996,7 +19996,7 @@
           <t>D | 342呎 (2房)
 $755万
 $22,085/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -20004,7 +20004,7 @@
           <t>E | 342呎 (2房)
 $717万
 $20,970/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -20012,7 +20012,7 @@
           <t>F | 341呎 (2房)
 $713万
 $20,911/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -20069,7 +20069,7 @@
           <t>B | 338呎 (2房)
 $708万
 $20,962/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>C | 344呎 (2房)
 $716万
 $20,800/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>D | 342呎 (2房)
 $713万
 $20,861/呎
-(26年-06月)</t>
+(26年-06月-13日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -20093,7 +20093,7 @@
           <t>E | 342呎 (2房)
 $715万
 $20,898/呎
-(26年-06月)</t>
+(26年-06月-13日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -20101,7 +20101,7 @@
           <t>F | 341呎 (2房)
 $748万
 $21,945/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -20125,7 +20125,7 @@
           <t>J | 395呎 (2房)
 $792万
 $20,041/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr"/>
@@ -20135,7 +20135,7 @@
           <t>M | 469呎 (2房)
 $976万
 $20,800/呎
-(26年-06月)</t>
+(26年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -20158,7 +20158,7 @@
           <t>B | 338呎 (2房)
 $706万
 $20,884/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>C | 344呎 (2房)
 $713万
 $20,740/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>D | 342呎 (2房)
 $711万
 $20,797/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -20182,7 +20182,7 @@
           <t>E | 342呎 (2房)
 $713万
 $20,834/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -20190,7 +20190,7 @@
           <t>F | 341呎 (2房)
 $721万
 $21,139/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -20239,7 +20239,7 @@
           <t>A | 585呎 (3房)
 $1198万
 $20,477/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -20247,7 +20247,7 @@
           <t>B | 338呎 (2房)
 $740万
 $21,901/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -20255,7 +20255,7 @@
           <t>C | 344呎 (2房)
 $710万
 $20,649/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -20263,7 +20263,7 @@
           <t>D | 342呎 (2房)
 $708万
 $20,714/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -20271,7 +20271,7 @@
           <t>E | 342呎 (2房)
 $710万
 $20,749/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -20336,7 +20336,7 @@
           <t>B | 338呎 (2房)
 $736万
 $21,785/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -20344,7 +20344,7 @@
           <t>C | 344呎 (2房)
 $706万
 $20,536/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -20352,7 +20352,7 @@
           <t>D | 342呎 (2房)
 $705万
 $20,603/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -20360,7 +20360,7 @@
           <t>E | 342呎 (2房)
 $746万
 $21,813/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -20402,7 +20402,7 @@
           <t>M | 469呎 (2房)
 $956万
 $20,390/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -20425,7 +20425,7 @@
           <t>B | 338呎 (2房)
 $694万
 $20,521/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -20433,7 +20433,7 @@
           <t>C | 344呎 (2房)
 $696万
 $20,231/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -20441,7 +20441,7 @@
           <t>D | 342呎 (2房)
 $700万
 $20,475/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -20449,7 +20449,7 @@
           <t>E | 342呎 (2房)
 $714万
 $20,873/呎
-(26年-07月)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>B | 338呎 (2房)
 $688万
 $20,357/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 344呎 (2房)
 $703万
 $20,449/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 342呎 (2房)
 $705万
 $20,618/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第4期.xlsx
+++ b/files/九龙-红磡-首岸第4期.xlsx
@@ -13848,7 +13848,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -20012,7 +20012,7 @@
           <t>F | 341呎 (2房)
 $713万
 $20,911/呎
-(26年-06月-26日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -20085,7 +20085,7 @@
           <t>D | 342呎 (2房)
 $713万
 $20,861/呎
-(26年-06月-13日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -20093,7 +20093,7 @@
           <t>E | 342呎 (2房)
 $715万
 $20,898/呎
-(26年-06月-13日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -20135,7 +20135,7 @@
           <t>M | 469呎 (2房)
 $976万
 $20,800/呎
-(26年-06月-13日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
     </row>
